--- a/AAII_Financials/Quarterly/KHOLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KHOLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="92">
   <si>
     <t>KHOLY</t>
   </si>
@@ -656,78 +656,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -773,8 +776,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -820,8 +826,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -867,8 +876,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -886,8 +898,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -933,8 +946,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -980,8 +996,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1027,8 +1046,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1074,8 +1096,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1090,8 +1115,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1137,8 +1163,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1184,8 +1213,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1203,8 +1235,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1250,8 +1283,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1297,8 +1333,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1344,8 +1383,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1391,8 +1433,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1438,8 +1483,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1485,8 +1533,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1532,8 +1583,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1579,8 +1633,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1626,8 +1683,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1673,8 +1733,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1720,8 +1783,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1767,8 +1833,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1814,8 +1883,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1861,8 +1933,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1908,8 +1983,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1955,60 +2033,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2026,8 +2110,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2045,431 +2130,459 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9346500</v>
+      </c>
+      <c r="E41" s="3">
         <v>8813900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8351800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9018300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7815300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8577000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11367700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9644500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8787700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8416300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14129800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9397500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8149400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8656800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13350600</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2259400</v>
+      </c>
+      <c r="E42" s="3">
         <v>2792800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2011200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1692500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1146600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1058100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2144900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1851500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2321100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2076700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1905300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1440600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>945500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1302400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2126000</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>18626600</v>
+      </c>
+      <c r="E43" s="3">
         <v>18459500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17703300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>19274600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>18305800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16633400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>21141300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>45208700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>44110400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39674600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>49826000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>35203300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>29801700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>34589100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>50464100</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5732300</v>
+      </c>
+      <c r="E44" s="3">
         <v>5006200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4922600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5228000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5370900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5420900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6314400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5441000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5391300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4562000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5762300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4283900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3731400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4209100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7519600</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6220000</v>
+      </c>
+      <c r="E45" s="3">
         <v>5157800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2545100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3076900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3085900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2937900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3828800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3613600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3212700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2937900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4404700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2857300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3182300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3051300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5357800</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>77482200</v>
+      </c>
+      <c r="E46" s="3">
         <v>74121300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>70207500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>74065800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>69841400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>66621000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>83914500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>69116700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>67064300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>60435500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>83604300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>54833500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>47519300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>53831700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>87366700</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17037700</v>
+      </c>
+      <c r="E47" s="3">
         <v>16560100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>17493100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>17248600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>16700500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>15023600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>21377500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>15997000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>15975300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>15655000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>22321900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>14340200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>12940800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>14031600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>23082800</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13873400</v>
+      </c>
+      <c r="E48" s="3">
         <v>13645100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13077300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12896500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12594800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>12340900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15760100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11629700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11075600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9688900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13468200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3805800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3644800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4128100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13659800</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5663500</v>
+      </c>
+      <c r="E49" s="3">
         <v>5710900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4670400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5147700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5037100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4973400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4875700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4191300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3907000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3414900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4162600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1121900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1120900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1267200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4605100</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2515,8 +2628,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2562,55 +2678,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5372800</v>
+      </c>
+      <c r="E52" s="3">
         <v>5020000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4345100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1259500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1219300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1314800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4333700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1322200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1298600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1229100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1586300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>946400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>933200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>950800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1988900</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2656,55 +2778,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>133600700</v>
+      </c>
+      <c r="E54" s="3">
         <v>129231300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>123768200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>122790300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>117047100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>110940600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>144631600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>112625200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>109456800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>100185400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>139584700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>85047400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>76694000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>86824400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>150556400</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2722,8 +2850,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2741,290 +2870,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9028800</v>
+      </c>
+      <c r="E57" s="3">
         <v>7462400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6876400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7210800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7086800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6612300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9273300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7160800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7829900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6002300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9112900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6566000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5008700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5029400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9055500</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>17523100</v>
+      </c>
+      <c r="E58" s="3">
         <v>17225200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>17543200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17108600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15248100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14373700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19478500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13727300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13855800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12975400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>17646300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10059000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9010300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10480200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>19896000</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9956200</v>
+      </c>
+      <c r="E59" s="3">
         <v>10464700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9837000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8044900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7636500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7259200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11027000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>51852800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>49896600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>45404000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>61955300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>43160700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>41048600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>46560900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>69911400</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>85628200</v>
+      </c>
+      <c r="E60" s="3">
         <v>85697400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>80523100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>82468500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>78383500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>73366000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>96392100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>75000600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>73332100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>65896400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>91095600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>61442200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>56263600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>63219200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>100901700</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16536000</v>
+      </c>
+      <c r="E61" s="3">
         <v>13901400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14000900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11999100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11217500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10516500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13063200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10253000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9244800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8497300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12078600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9043300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7446200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8315000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13436900</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>551900</v>
+      </c>
+      <c r="E62" s="3">
         <v>749500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>825900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1013300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1055700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>797000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>664400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>977100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1002300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>991600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1447600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1007800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1064200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1079000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1746100</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3070,8 +3218,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3117,8 +3268,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3164,55 +3318,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>105909800</v>
+      </c>
+      <c r="E66" s="3">
         <v>103511700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>98338300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>97784600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>92948400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>86777600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>112854500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>88006600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>85199800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>76880100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>106664400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>72306900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>65590700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>73524500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>117961800</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3230,8 +3390,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3277,8 +3438,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3324,8 +3488,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3371,8 +3538,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3418,55 +3588,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16084400</v>
+      </c>
+      <c r="E72" s="3">
         <v>15411300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>14826400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14545600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13969300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>14084400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18023100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13333800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12882100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12518200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17386600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7079000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6130200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7259200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15653500</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3512,8 +3688,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3559,8 +3738,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3606,55 +3788,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16988300</v>
+      </c>
+      <c r="E76" s="3">
         <v>16065100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15765400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15498800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14950300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15133500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19563500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14907300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14496700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14208400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19829900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7812100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6924700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8263400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19545300</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3700,60 +3888,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3799,8 +3993,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3818,55 +4015,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>463700</v>
+      </c>
+      <c r="E83" s="3">
         <v>415200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>753800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>473700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>463700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>292600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>456900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>279200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>275400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>359600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>841000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>97200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>93900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>97500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>95200</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3912,8 +4113,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3959,8 +4163,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4006,8 +4213,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4053,8 +4263,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4100,55 +4313,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1845500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1716200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1285800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>104800</v>
       </c>
-      <c r="G89" s="3">
-        <v>-946200</v>
-      </c>
       <c r="H89" s="3">
+        <v>-1254200</v>
+      </c>
+      <c r="I89" s="3">
         <v>-462200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1076300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1579100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4312200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2504600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2193100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4219600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5917200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8060900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4385000</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4166,55 +4385,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-793500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-534200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-708800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-588600</v>
       </c>
-      <c r="G91" s="3">
-        <v>-677000</v>
-      </c>
       <c r="H91" s="3">
+        <v>-900900</v>
+      </c>
+      <c r="I91" s="3">
         <v>-725400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1288500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-739600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1008000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-749600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1133300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-777900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1000700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-919800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1760300</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4260,8 +4483,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4307,55 +4533,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-124100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-927600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2375600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1002500</v>
       </c>
-      <c r="G94" s="3">
-        <v>-1631900</v>
-      </c>
       <c r="H94" s="3">
+        <v>-2150300</v>
+      </c>
+      <c r="I94" s="3">
         <v>622100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1530400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>154900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-576700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2813400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1483400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-444300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5547600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1992200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1356000</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4373,55 +4605,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>106600</v>
+      </c>
+      <c r="E96" s="3">
         <v>634500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>19600</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
-        <v>738500</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3">
+        <v>975600</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
         <v>42200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>70000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>972900</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
         <v>27600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>38600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>35300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>570600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4467,8 +4703,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4514,8 +4753,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4561,145 +4803,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3555700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-257300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2537200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3061000</v>
       </c>
-      <c r="G100" s="3">
-        <v>1375400</v>
-      </c>
       <c r="H100" s="3">
+        <v>1814200</v>
+      </c>
+      <c r="I100" s="3">
         <v>-315600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-346700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1061300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1843500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1510900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1152500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-563400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>697800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3229100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-151300</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>723700</v>
+      </c>
+      <c r="E101" s="3">
         <v>709800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>74000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>576500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-367500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1332100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>378800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>615300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3030500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>372900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2085600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>595600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>770800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>989000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3010000</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1935300</v>
+      </c>
+      <c r="E102" s="3">
         <v>708900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-887300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2525900</v>
       </c>
-      <c r="G102" s="3">
-        <v>-659700</v>
-      </c>
       <c r="H102" s="3">
+        <v>-866600</v>
+      </c>
+      <c r="I102" s="3">
         <v>554200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-726800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3371900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1524500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2475000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2241000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3827100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4098000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3212500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4963400</v>
       </c>
     </row>
